--- a/examples/excel/charts/charts-advanced.xlsx
+++ b/examples/excel/charts/charts-advanced.xlsx
@@ -3,9 +3,9 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="1-Scatter &amp; Bubble" sheetId="2" r:id="Rc37791d4a192405d"/>
-    <x:sheet name="2-Combo &amp; Radar" sheetId="3" r:id="Rb6f0c722e762409b"/>
-    <x:sheet name="3-Stock &amp; Radar" sheetId="4" r:id="R7c837321ad9645ae"/>
+    <x:sheet name="1-Scatter &amp; Bubble" sheetId="2" r:id="Rb12d48140874487d"/>
+    <x:sheet name="2-Combo &amp; Radar" sheetId="3" r:id="R7c243aef742141df"/>
+    <x:sheet name="3-Stock &amp; Radar" sheetId="4" r:id="Rb8633c43deb54a64"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43,7 +43,11 @@
             <c:v>SeriesA</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -103,7 +107,11 @@
             <c:v>SeriesB</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -232,6 +240,14 @@
           <c:tx>
             <c:v>Open</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="6"/>
@@ -286,6 +302,14 @@
           <c:tx>
             <c:v>High</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="6"/>
@@ -340,6 +364,14 @@
           <c:tx>
             <c:v>Low</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="6"/>
@@ -394,6 +426,14 @@
           <c:tx>
             <c:v>Close</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="6"/>
@@ -442,6 +482,24 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:hiLowLines/>
+        <c:upDownBars>
+          <c:gapWidth val="150"/>
+          <c:upBars>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4CAF50"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:upBars>
+          <c:downBars>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="F44336"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:downBars>
+        </c:upDownBars>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:stockChart>
@@ -529,11 +587,11 @@
             <c:v>BrandX</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4">
-                <a:alpha val="60000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -584,11 +642,11 @@
             <c:v>BrandY</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47">
-                <a:alpha val="60000"/>
-              </a:srgbClr>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -806,7 +864,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US" sz="1400" b="1"/>
-                  <a:t>Market</a:t>
+                  <a:t>Market Size</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -895,6 +953,13 @@
           <c:tx>
             <c:v>Growth</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
           <c:marker>
             <c:symbol val="diamond"/>
             <c:size val="7"/>
@@ -1096,8 +1161,16 @@
             <c:v>Squares</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="9"/>
+          </c:marker>
           <c:xVal>
             <c:numLit>
               <c:ptCount val="5"/>
@@ -1138,9 +1211,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:marker>
-            <c:size val="9"/>
-          </c:marker>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1149,8 +1219,16 @@
             <c:v>Triangles</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="9"/>
+          </c:marker>
           <c:xVal>
             <c:numLit>
               <c:ptCount val="5"/>
@@ -1191,9 +1269,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:marker>
-            <c:size val="9"/>
-          </c:marker>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1202,8 +1277,16 @@
             <c:v>Stars</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
+          <c:marker>
+            <c:symbol val="star"/>
+            <c:size val="9"/>
+          </c:marker>
           <c:xVal>
             <c:numLit>
               <c:ptCount val="5"/>
@@ -1244,9 +1327,6 @@
               </c:pt>
             </c:numLit>
           </c:yVal>
-          <c:marker>
-            <c:size val="9"/>
-          </c:marker>
         </c:ser>
         <c:axId val="1"/>
         <c:axId val="2"/>
@@ -1664,6 +1744,7 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -1677,9 +1758,11 @@
             <c:v>Growth</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -1729,7 +1812,6 @@
             </c:numLit>
           </c:val>
         </c:ser>
-        <c:marker val="1"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:lineChart>
@@ -1886,19 +1968,13 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
-        <c:marker val="1"/>
-        <c:axId val="1"/>
-        <c:axId val="2"/>
-      </c:lineChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -1906,9 +1982,11 @@
             <c:v>AvgPrice</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2006,7 +2084,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -2166,9 +2244,11 @@
             <c:v>Lines</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2350,9 +2430,11 @@
             <c:v>AthleteA</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2403,9 +2485,11 @@
             <c:v>AthleteB</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2456,9 +2540,11 @@
             <c:v>AthleteC</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="70AD47"/>
-            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:cat>
             <c:strLit>
@@ -2578,6 +2664,14 @@
           <c:tx>
             <c:v>Open</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="5"/>
@@ -2626,6 +2720,14 @@
           <c:tx>
             <c:v>High</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="5"/>
@@ -2674,6 +2776,14 @@
           <c:tx>
             <c:v>Low</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="5"/>
@@ -2722,6 +2832,14 @@
           <c:tx>
             <c:v>Close</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:strLit>
               <c:ptCount val="5"/>
@@ -2764,6 +2882,24 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:hiLowLines/>
+        <c:upDownBars>
+          <c:gapWidth val="150"/>
+          <c:upBars>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4CAF50"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:upBars>
+          <c:downBars>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="F44336"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:downBars>
+        </c:upDownBars>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:stockChart>
@@ -2872,7 +3008,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rad501bb953434997"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc371e28d969f472e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2902,7 +3038,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9be3cc0eca144555"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R134eb6eba88244fb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2932,7 +3068,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3a11d45853ad40df"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re884c4c1ba924e92"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2962,7 +3098,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R68f2b02e65634d1e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R969ffe7ede794823"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2997,7 +3133,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1416c26c4857491e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R97a754b5731743ba"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3027,7 +3163,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R332627d345ba40bb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R756ac2cf737542d3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3057,7 +3193,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdfd40877baaf4c9d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf90fa9ba91814d78"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3087,7 +3223,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R74198d3d54794d76"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf4d88efbb6904fe8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3122,7 +3258,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1f03d3aa69444602"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4b76f89369304068"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3152,7 +3288,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raff3146bae464be1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R68974fed67404ee9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3182,7 +3318,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R076d6721163846e7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R16d1d76463644c10"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3212,13 +3348,122 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra0aea936b5a641e8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae224a387bee4c8f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3230,20 +3475,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf926c8067541468f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3d1e01a800a4cba"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7593429e6b8e4880"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb394b5a3fef54630"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e0a803731ca482b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00fa899511134147"/>
 </x:worksheet>
 </file>